--- a/data/trans_dic/IQ2608_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IQ2608_R3-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>60,67%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>86,98%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>83,6%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>69,33%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>54,04%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>79,09%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>81,79%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>66,92%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>60,67%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>86,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,6%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,97; 61,64</t>
+          <t>53,1; 68,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,38; 85,52</t>
+          <t>80,1; 92,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,73; 88,5</t>
+          <t>76,46; 88,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,95; 79,05</t>
+          <t>54,07; 81,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,69; 69,05</t>
+          <t>46,59; 61,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,73; 92,26</t>
+          <t>71,24; 85,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,03; 89,11</t>
+          <t>73,36; 87,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,59; 82,38</t>
+          <t>51,42; 78,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51,83; 62,79</t>
+          <t>51,65; 63,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78,21; 87,53</t>
+          <t>77,44; 87,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77,87; 87,17</t>
+          <t>77,72; 87,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,27; 78,68</t>
+          <t>56,95; 77,32</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>69,29%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>87,57%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86,44%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>61,55%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>62,01%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>87,85%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>85,24%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>69,81%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>69,29%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>86,44%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,89; 70,77</t>
+          <t>60,6; 77,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,14; 92,97</t>
+          <t>81,08; 92,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,02; 90,5</t>
+          <t>80,61; 91,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54,52; 83,01</t>
+          <t>42,8; 77,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,91; 77,01</t>
+          <t>53,27; 70,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,96; 92,42</t>
+          <t>80,63; 92,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,63; 90,95</t>
+          <t>78,61; 90,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,75; 77,92</t>
+          <t>53,19; 83,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59,11; 70,81</t>
+          <t>59,72; 71,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83,24; 91,24</t>
+          <t>83,22; 91,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81,53; 89,32</t>
+          <t>81,43; 89,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,29; 76,94</t>
+          <t>53,73; 76,5</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>59,24%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84,78%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>76,97%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>73,53%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>63,99%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>83,11%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>72,35%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>53,12%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>59,24%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,97%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,87; 73,26</t>
+          <t>51,36; 67,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,63; 88,58</t>
+          <t>77,09; 90,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,61; 80,47</t>
+          <t>68,32; 84,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,48; 77,09</t>
+          <t>50,68; 89,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,71; 66,98</t>
+          <t>54,1; 72,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,63; 90,91</t>
+          <t>76,25; 88,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,62; 84,01</t>
+          <t>61,78; 80,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,56; 89,25</t>
+          <t>28,15; 75,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,79; 66,57</t>
+          <t>54,84; 66,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78,97; 88,12</t>
+          <t>78,98; 88,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68,45; 80,43</t>
+          <t>68,07; 80,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,32; 78,68</t>
+          <t>47,42; 78,44</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>66,61%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>82,52%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>86,84%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>78,2%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>66,52%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>81,01%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>81,44%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73,91%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>66,61%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>82,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,84%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,92%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,24; 71,91</t>
+          <t>61,2; 71,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,98; 85,16</t>
+          <t>78,23; 86,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,47; 85,49</t>
+          <t>82,74; 90,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62,11; 85,1</t>
+          <t>65,42; 88,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,92; 71,56</t>
+          <t>61,16; 71,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,93; 86,68</t>
+          <t>75,7; 85,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,64; 90,46</t>
+          <t>76,99; 85,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,28; 87,94</t>
+          <t>60,76; 84,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,98; 70,06</t>
+          <t>62,89; 70,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78,57; 84,78</t>
+          <t>78,57; 84,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81,05; 86,67</t>
+          <t>80,93; 86,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,69; 83,95</t>
+          <t>66,21; 83,56</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>60,84%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>73,1%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>85,25%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70,54%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>58,04%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>75,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>82,82%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>63,15%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>60,84%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>73,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>85,25%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>49,94; 66,32</t>
+          <t>53,81; 67,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,36; 80,25</t>
+          <t>66,89; 79,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,72; 87,56</t>
+          <t>79,22; 89,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,1; 79,81</t>
+          <t>57,36; 82,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>53,54; 67,28</t>
+          <t>50,05; 65,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,94; 78,68</t>
+          <t>68,22; 80,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,04; 89,65</t>
+          <t>77,23; 88,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,15; 82,73</t>
+          <t>41,42; 74,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54,39; 64,61</t>
+          <t>54,33; 64,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69,7; 78,37</t>
+          <t>69,27; 77,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80,41; 87,35</t>
+          <t>80,31; 87,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,86; 78,3</t>
+          <t>56,04; 75,92</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64,13%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82,26%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>72,24%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51,46%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>50,74%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>87,6%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>69,66%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>64,13%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,24%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,9; 60,83</t>
+          <t>54,7; 72,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77,75; 93,94</t>
+          <t>73,72; 89,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59,37; 78,63</t>
+          <t>62,16; 80,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,56; 69,97</t>
+          <t>33,88; 69,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54,53; 73,35</t>
+          <t>41,25; 60,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,96; 89,1</t>
+          <t>77,33; 93,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,16; 80,56</t>
+          <t>59,81; 78,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38,11; 73,34</t>
+          <t>25,49; 72,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,92; 63,73</t>
+          <t>50,78; 63,84</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78,31; 89,05</t>
+          <t>78,7; 89,29</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64,16; 77,26</t>
+          <t>64,33; 77,1</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39,27; 67,11</t>
+          <t>35,17; 65,51</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>63,7%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>82,11%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>83,55%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>69,13%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>60,36%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>81,18%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>80,43%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>65,81%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>63,7%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>82,11%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>83,55%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,88; 63,4</t>
+          <t>60,49; 66,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>78,64; 83,91</t>
+          <t>79,71; 84,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,97; 82,78</t>
+          <t>80,99; 85,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58,03; 72,14</t>
+          <t>62,69; 75,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,83; 66,45</t>
+          <t>56,68; 63,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,57; 84,44</t>
+          <t>78,51; 83,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,03; 85,82</t>
+          <t>77,66; 82,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63,76; 75,91</t>
+          <t>58,51; 71,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60,03; 64,23</t>
+          <t>60,02; 64,26</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79,98; 83,36</t>
+          <t>79,81; 83,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80,42; 83,7</t>
+          <t>80,33; 83,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,3; 72,66</t>
+          <t>62,53; 71,48</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>57627</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>74086</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>81226</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25502</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>54629</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>68524</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>65412</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20126</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>57627</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74086</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81226</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26413</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46539</t>
+          <t>45420</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>46468; 62306</t>
+          <t>50438; 65526</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>61849; 74097</t>
+          <t>68227; 78466</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58964; 70772</t>
+          <t>74294; 86233</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15323; 23775</t>
+          <t>19890; 29961</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50049; 65584</t>
+          <t>47094; 62504</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67913; 78580</t>
+          <t>61723; 74110</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74845; 86588</t>
+          <t>58671; 70327</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20566; 31034</t>
+          <t>15489; 23763</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>101627; 123108</t>
+          <t>101271; 123714</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134385; 150394</t>
+          <t>133065; 149893</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137932; 154405</t>
+          <t>137668; 154837</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39475; 53307</t>
+          <t>38102; 51735</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>59572</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>81745</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96303</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12254</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>52246</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>80218</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>88003</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17002</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>59572</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81745</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96303</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>29482</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45408; 59628</t>
+          <t>52097; 66426</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75003; 84896</t>
+          <t>75684; 86311</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81577; 93430</t>
+          <t>89806; 101518</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13279; 20217</t>
+          <t>8521; 15511</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52364; 66210</t>
+          <t>44889; 59814</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75571; 86273</t>
+          <t>73623; 84382</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88714; 101319</t>
+          <t>81152; 93353</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8658; 16556</t>
+          <t>13229; 20672</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100632; 120544</t>
+          <t>101670; 122289</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>153719; 168478</t>
+          <t>153672; 168541</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>175008; 191710</t>
+          <t>174775; 191768</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24302; 35089</t>
+          <t>24063; 34260</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>58369</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70234</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>57034</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11936</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>42272</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>69311</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>44744</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6140</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>58369</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70234</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>57034</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>18109</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34925; 48393</t>
+          <t>50598; 66309</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>63074; 73875</t>
+          <t>63862; 74584</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38099; 49761</t>
+          <t>50626; 62479</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3177; 8910</t>
+          <t>8226; 14509</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50946; 65986</t>
+          <t>35740; 48196</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64310; 75316</t>
+          <t>63593; 74039</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50850; 62247</t>
+          <t>38203; 49754</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9463; 15769</t>
+          <t>3335; 8897</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90177; 109560</t>
+          <t>90260; 109765</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>131283; 146492</t>
+          <t>131305; 146648</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>93052; 109336</t>
+          <t>92536; 109072</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14123; 22996</t>
+          <t>13316; 22025</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>275</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>130845</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>181305</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>182033</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33133</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>130502</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>161427</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>179252</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28203</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>130845</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>181305</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>182033</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36304</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64507</t>
+          <t>59697</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>120156; 141082</t>
+          <t>120222; 140499</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>151399; 169695</t>
+          <t>171881; 189843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>170512; 188160</t>
+          <t>173446; 189731</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23702; 32472</t>
+          <t>27717; 37450</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>119666; 140577</t>
+          <t>119985; 140296</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>171207; 190449</t>
+          <t>150851; 170471</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>173248; 189622</t>
+          <t>169452; 188218</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30026; 41080</t>
+          <t>22038; 30610</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>247282; 275074</t>
+          <t>246943; 275333</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>329188; 355197</t>
+          <t>329203; 355158</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>348283; 372429</t>
+          <t>347794; 373164</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>56598; 71252</t>
+          <t>52068; 65707</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>170</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>75780</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>101376</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>121146</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>27860</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>58873</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>108174</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>111822</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14642</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>75780</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>101376</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>121146</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30038</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44680</t>
+          <t>39457</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50666; 67278</t>
+          <t>67029; 84274</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>98599; 115744</t>
+          <t>92769; 110357</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103596; 118224</t>
+          <t>112571; 127212</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10457; 18503</t>
+          <t>22655; 32478</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>66693; 83810</t>
+          <t>50772; 66479</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91442; 109113</t>
+          <t>98389; 115889</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>113745; 127399</t>
+          <t>104280; 118837</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24365; 34665</t>
+          <t>8260; 14883</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>122933; 146035</t>
+          <t>122800; 146338</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>197201; 221708</t>
+          <t>195981; 220526</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>222826; 242085</t>
+          <t>222562; 242763</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37659; 50962</t>
+          <t>33305; 45120</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>44570</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>58193</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>48996</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10711</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>37601</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>45558</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>42136</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6248</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>44570</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>58193</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>48996</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>17406</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31050; 45075</t>
+          <t>38017; 50470</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40438; 48858</t>
+          <t>52149; 63009</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35915; 47565</t>
+          <t>42162; 54298</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3198; 9109</t>
+          <t>7053; 14536</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37898; 50978</t>
+          <t>30569; 45102</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52323; 63028</t>
+          <t>40215; 48693</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42159; 54641</t>
+          <t>36179; 47740</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8972; 17268</t>
+          <t>3481; 9905</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>73124; 91513</t>
+          <t>72916; 91671</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96132; 109308</t>
+          <t>96601; 109604</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82327; 99137</t>
+          <t>82551; 98933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14360; 24539</t>
+          <t>12123; 22584</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>565</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>767</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>806</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>145</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>840</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>426763</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>566939</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>586738</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>121397</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>376124</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>533213</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>531369</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>92361</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>426763</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>566939</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>586738</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>131934</t>
+          <t>88174</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>224296</t>
+          <t>209571</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>354455; 395092</t>
+          <t>405261; 445432</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>516541; 551187</t>
+          <t>550395; 582567</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>515139; 546917</t>
+          <t>568764; 602383</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>81451; 101255</t>
+          <t>110089; 132372</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>407573; 445219</t>
+          <t>353185; 394430</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>549455; 583081</t>
+          <t>515737; 547895</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>568997; 602636</t>
+          <t>513082; 547966</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>120347; 143273</t>
+          <t>79996; 97092</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>776305; 830603</t>
+          <t>776163; 830979</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1077561; 1123123</t>
+          <t>1075341; 1122143</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1095993; 1140677</t>
+          <t>1094762; 1141010</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>208333; 239131</t>
+          <t>195306; 223249</t>
         </is>
       </c>
     </row>
